--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6794708</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6794707</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,8 +990,18 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6794715</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ4"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6794708</v>
+        <v>135784709</v>
       </c>
       <c r="B2" t="n">
-        <v>106229</v>
+        <v>79107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tossåsen, Hjd</t>
+          <t>Lövdalen, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>415241</v>
+        <v>415301</v>
       </c>
       <c r="R2" t="n">
-        <v>6971543</v>
+        <v>6971466</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,69 +765,65 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6794708</t>
+          <t>https://artportalen.se/Sighting/135784709</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6794707</v>
+        <v>135784711</v>
       </c>
       <c r="B3" t="n">
-        <v>103683</v>
+        <v>92227</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222002</v>
+        <v>1503</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tossåsen, Hjd</t>
+          <t>Lövdalen, Hjd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>415241</v>
+        <v>415319</v>
       </c>
       <c r="R3" t="n">
-        <v>6971543</v>
+        <v>6971444</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -871,69 +867,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hugo Ström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6794707</t>
+          <t>https://artportalen.se/Sighting/135784711</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6794715</v>
+        <v>135784710</v>
       </c>
       <c r="B4" t="n">
-        <v>104628</v>
+        <v>93345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222412</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tossåsen, Hjd</t>
+          <t>Lövdalen, Hjd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>415427</v>
+        <v>415311</v>
       </c>
       <c r="R4" t="n">
-        <v>6971592</v>
+        <v>6971457</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -957,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2012-06-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -977,22 +969,749 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784710</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135784712</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80060</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>415320</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6971460</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784712</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>135784706</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>415176</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6971428</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Klen gran med helt avskalad bark.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784706</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135784708</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>415290</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6971459</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784708</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6794708</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106229</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tossåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>415241</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6971543</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Hugo Ström</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Hugo Ström</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr">
+      <c r="AY8" t="inlineStr">
         <is>
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6794708</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6794707</v>
+      </c>
+      <c r="B9" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tossåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>415241</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6971543</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6794707</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>6794715</v>
+      </c>
+      <c r="B10" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tossåsen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>415427</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6971592</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2012-06-11</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Hugo Ström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/6794715</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135784707</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lövdalen, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>415199</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6971418</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Storsjö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alexander Singer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135784707</t>
         </is>
       </c>
     </row>
@@ -1001,6 +1720,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135784711</v>
       </c>
       <c r="B3" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784710</v>
       </c>
       <c r="B4" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784709</v>
       </c>
       <c r="B2" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784711</v>
       </c>
       <c r="B3" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784710</v>
       </c>
       <c r="B4" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784712</v>
       </c>
       <c r="B5" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784706</v>
       </c>
       <c r="B6" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>135784708</v>
       </c>
       <c r="B7" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>135784707</v>
       </c>
       <c r="B11" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784709</v>
       </c>
       <c r="B2" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784711</v>
       </c>
       <c r="B3" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784710</v>
       </c>
       <c r="B4" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784712</v>
       </c>
       <c r="B5" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>135784707</v>
       </c>
       <c r="B11" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135784711</v>
       </c>
       <c r="B3" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784710</v>
       </c>
       <c r="B4" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784709</v>
       </c>
       <c r="B2" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784711</v>
       </c>
       <c r="B3" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784710</v>
       </c>
       <c r="B4" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784712</v>
       </c>
       <c r="B5" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784706</v>
       </c>
       <c r="B6" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>135784708</v>
       </c>
       <c r="B7" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>135784707</v>
       </c>
       <c r="B11" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784709</v>
       </c>
       <c r="B2" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784711</v>
       </c>
       <c r="B3" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784710</v>
       </c>
       <c r="B4" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784712</v>
       </c>
       <c r="B5" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784706</v>
       </c>
       <c r="B6" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>135784708</v>
       </c>
       <c r="B7" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>135784707</v>
       </c>
       <c r="B11" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784709</v>
       </c>
       <c r="B2" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784711</v>
       </c>
       <c r="B3" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784710</v>
       </c>
       <c r="B4" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784712</v>
       </c>
       <c r="B5" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784706</v>
       </c>
       <c r="B6" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>135784708</v>
       </c>
       <c r="B7" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>135784707</v>
       </c>
       <c r="B11" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784709</v>
       </c>
       <c r="B2" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784711</v>
       </c>
       <c r="B3" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784710</v>
       </c>
       <c r="B4" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784712</v>
       </c>
       <c r="B5" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>135784707</v>
       </c>
       <c r="B11" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135784709</v>
       </c>
       <c r="B2" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135784711</v>
       </c>
       <c r="B3" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784710</v>
       </c>
       <c r="B4" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135784712</v>
       </c>
       <c r="B5" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>135784706</v>
       </c>
       <c r="B6" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>135784708</v>
       </c>
       <c r="B7" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>135784707</v>
       </c>
       <c r="B11" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37062-2025 artfynd.xlsx
+++ b/artfynd/A 37062-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>135784711</v>
       </c>
       <c r="B3" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135784710</v>
       </c>
       <c r="B4" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
